--- a/data/profit-report-template.xlsx
+++ b/data/profit-report-template.xlsx
@@ -5,18 +5,6 @@
   <sheets>
     <sheet name="주차별 매출이익 보고서" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">구매현황!$A$2:$N$77</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'그 외 매출액'!$A$2:$J$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">불량차감!$A$2:$J$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">재고잔량!$B$89:$O$129</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'주차별 매출이익 보고서'!$B$6:$U$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">판매현황!$A$3:$I$716</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">품목리스트!$A$1:$I$3054</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">불량차감!$A$1:$M$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">재고잔량!$B$1:$G$56</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'주차별 매출이익 보고서'!$A$1:$U$33</definedName>
-  </definedNames>
 </workbook>
 </file>
 
